--- a/PCB/PowerDistributionModule2027/PDM_Place.xlsx
+++ b/PCB/PowerDistributionModule2027/PDM_Place.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://svsu0-my.sharepoint.com/personal/wodougla_svsu_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4a56d338d63da0fa/Desktop/CFR-2027/PCB/PowerDistributionModule2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{F9EED812-62E5-4EF1-A042-88EA43E58C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD77D7F0-730B-4BE2-8CDC-327528804073}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{F9EED812-62E5-4EF1-A042-88EA43E58C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD7C414-1DBF-434B-975B-79E5AD771185}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{D85DCD4B-4810-477B-941E-B67A1F7CBA2D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D85DCD4B-4810-477B-941E-B67A1F7CBA2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -537,15 +537,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D68785-242A-42B1-9468-D46F0046B09D}">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.734375" customWidth="1"/>
-    <col min="4" max="4" width="5.7890625" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="19.68359375" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -576,10 +576,10 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -593,10 +593,10 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -610,10 +610,10 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -627,10 +627,10 @@
         <v>41</v>
       </c>
       <c r="E5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -644,10 +644,10 @@
         <v>41</v>
       </c>
       <c r="E6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -661,10 +661,10 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -698,12 +698,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>100.2375</v>
+        <v>99.087500000000006</v>
       </c>
       <c r="C10">
         <v>-55.8</v>
@@ -712,15 +712,15 @@
         <v>41</v>
       </c>
       <c r="E10">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>124.75</v>
+        <v>123.6</v>
       </c>
       <c r="C11">
         <v>-53.715000000000003</v>
@@ -729,15 +729,15 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>99.65</v>
+        <v>98.5</v>
       </c>
       <c r="C12">
         <v>-93.795000000000002</v>
@@ -746,15 +746,15 @@
         <v>41</v>
       </c>
       <c r="E12">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>128.27500000000001</v>
+        <v>127.125</v>
       </c>
       <c r="C13">
         <v>-93.1</v>
@@ -763,15 +763,15 @@
         <v>41</v>
       </c>
       <c r="E13">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>199.52500000000001</v>
+        <v>200.67500000000001</v>
       </c>
       <c r="C14">
         <v>-52.95</v>
@@ -780,15 +780,15 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <v>171.72499999999999</v>
+        <v>172.875</v>
       </c>
       <c r="C15">
         <v>-53.05</v>
@@ -797,10 +797,10 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -817,7 +817,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -834,7 +834,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -851,7 +851,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -868,7 +868,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -885,7 +885,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -902,7 +902,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -919,7 +919,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -936,7 +936,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -953,7 +953,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -970,7 +970,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -987,7 +987,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
